--- a/output/quickfixclose14_portfolio_daily.xlsx
+++ b/output/quickfixclose14_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$186</f>
+              <f>'equity_curve'!$A$2:$A$188</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$186</f>
+              <f>'equity_curve'!$B$2:$B$188</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>229,267.47</t>
+          <t>226,767.75</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+129.27%</t>
+          <t>+126.77%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>236,863  (+136.86%)</t>
+          <t>234,559  (+134.56%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4,222  (7.6 pts of return)</t>
+          <t>4,490  (7.8 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6.0x</t>
+          <t>5.8x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>23.4%</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-1,382  (-1.27%)</t>
+          <t>-1,402  (-1.27%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-31</t>
+          <t>2025-12-18 -&gt; 2026-08-04</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5783,22 +5783,70 @@
         <v>46234</v>
       </c>
       <c r="B186" s="5" t="n">
-        <v>229267.47</v>
+        <v>229474.98</v>
       </c>
       <c r="C186" s="5" t="n">
+        <v>8517.15</v>
+      </c>
+      <c r="D186" s="5" t="n">
+        <v>220957.83</v>
+      </c>
+      <c r="E186" t="n">
+        <v>4</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, NY_Natural_Gas_Futures, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B187" s="5" t="n">
+        <v>229474.98</v>
+      </c>
+      <c r="C187" s="5" t="n">
+        <v>8517.15</v>
+      </c>
+      <c r="D187" s="5" t="n">
+        <v>220957.83</v>
+      </c>
+      <c r="E187" t="n">
+        <v>4</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, NY_Natural_Gas_Futures, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B188" s="5" t="n">
+        <v>226767.75</v>
+      </c>
+      <c r="C188" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="D186" s="5" t="n">
-        <v>229267.47</v>
-      </c>
-      <c r="E186" t="n">
+      <c r="D188" s="5" t="n">
+        <v>226767.75</v>
+      </c>
+      <c r="E188" t="n">
         <v>0</v>
       </c>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); NY_Natural_Gas_Futures open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); NY_Natural_Gas_Futures stop (-2,589); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -9896,7 +9944,7 @@
         <v>-43.45</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>283112.39</v>
+        <v>278864.08</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -9920,14 +9968,22 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>4</v>
+      </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G81" t="n">
-        <v>0.04</v>
+        <v>0.16</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.04</v>
+        <v>-1.16</v>
       </c>
       <c r="I81" s="5" t="n">
         <v>272887.26</v>
@@ -9936,14 +9992,14 @@
         <v>3793.13</v>
       </c>
       <c r="K81" s="6" t="n">
-        <v>-151.73</v>
+        <v>-4400.03</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>283155.84</v>
+        <v>278907.53</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>stop</t>
         </is>
       </c>
     </row>

--- a/output/quickfixclose14_portfolio_daily.xlsx
+++ b/output/quickfixclose14_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$188</f>
+              <f>'equity_curve'!$A$2:$A$190</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$188</f>
+              <f>'equity_curve'!$B$2:$B$190</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>226,767.75</t>
+          <t>226,755.85</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+126.77%</t>
+          <t>+126.76%</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4,490  (7.8 pts of return)</t>
+          <t>4,502  (7.8 pts of return)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-04</t>
+          <t>2025-12-18 -&gt; 2026-08-06</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5831,22 +5831,82 @@
         <v>46238</v>
       </c>
       <c r="B188" s="5" t="n">
-        <v>226767.75</v>
+        <v>226885.97</v>
       </c>
       <c r="C188" s="5" t="n">
-        <v>-0</v>
+        <v>6285.25</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>226767.75</v>
+        <v>220600.72</v>
       </c>
       <c r="E188" t="n">
-        <v>0</v>
-      </c>
-      <c r="F188" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); NY_Natural_Gas_Futures stop (-2,589); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
+          <t>NY_Natural_Gas_Futures stop (-2,589)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B189" s="5" t="n">
+        <v>226885.97</v>
+      </c>
+      <c r="C189" s="5" t="n">
+        <v>12837.31</v>
+      </c>
+      <c r="D189" s="5" t="n">
+        <v>214048.66</v>
+      </c>
+      <c r="E189" t="n">
+        <v>6</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures short (risk 2,206); Nasdaq_100_E_mini short (risk 2,184); S_P_500_E_mini short (risk 2,162)</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B190" s="5" t="n">
+        <v>226755.85</v>
+      </c>
+      <c r="C190" s="5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>226755.85</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 2,140)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -5862,7 +5922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -9858,7 +9918,7 @@
         <v>-67.45</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>283395.69</v>
+        <v>278995.65</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -9901,7 +9961,7 @@
         <v>-88.13</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>283307.56</v>
+        <v>278907.53</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -9944,7 +10004,7 @@
         <v>-43.45</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>278864.08</v>
+        <v>278844.03</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -9995,11 +10055,183 @@
         <v>-4400.03</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>278907.53</v>
+        <v>279063.1</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
           <t>stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>268487.23</v>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>3731.97</v>
+      </c>
+      <c r="K82" s="6" t="n">
+        <v>-12.96</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>278888.25</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Nasdaq_100_E_mini</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>264755.26</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>3680.1</v>
+      </c>
+      <c r="K83" s="6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>278901.21</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>261075.16</v>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>3628.94</v>
+      </c>
+      <c r="K84" s="6" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>278887.48</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>257446.21</v>
+      </c>
+      <c r="J85" s="5" t="n">
+        <v>3578.5</v>
+      </c>
+      <c r="K85" s="6" t="n">
+        <v>-6.12</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>278901.41</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
         </is>
       </c>
     </row>

--- a/output/quickfixclose14_portfolio_daily.xlsx
+++ b/output/quickfixclose14_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$190</f>
+              <f>'equity_curve'!$A$2:$A$191</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$190</f>
+              <f>'equity_curve'!$B$2:$B$191</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>226,755.85</t>
+          <t>224,590.43</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+126.76%</t>
+          <t>+124.59%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>234,559  (+134.56%)</t>
+          <t>232,346  (+132.35%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4,502  (7.8 pts of return)</t>
+          <t>4,527  (7.8 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5.8x</t>
+          <t>5.7x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.1%</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5.3 bars</t>
+          <t>5.2 bars</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-1,402  (-1.27%)</t>
+          <t>-1,415  (-1.27%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-06</t>
+          <t>2025-12-18 -&gt; 2026-08-07</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H190"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5887,26 +5887,54 @@
         <v>46240</v>
       </c>
       <c r="B190" s="5" t="n">
-        <v>226755.85</v>
+        <v>226885.97</v>
       </c>
       <c r="C190" s="5" t="n">
+        <v>14977.8</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>211908.17</v>
+      </c>
+      <c r="E190" t="n">
+        <v>7</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, Gold_Futures_COMEX, NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 2,140)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B191" s="5" t="n">
+        <v>224590.43</v>
+      </c>
+      <c r="C191" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="D190" s="5" t="n">
-        <v>226755.85</v>
-      </c>
-      <c r="E190" t="n">
+      <c r="D191" s="5" t="n">
+        <v>224590.43</v>
+      </c>
+      <c r="E191" t="n">
         <v>0</v>
       </c>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>Gold_Futures_COMEX short (risk 2,140)</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures short (risk 2,119); NY_Palladium_Futures short (risk 2,098)</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); Gold_Futures_COMEX stop (-2,155); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Copper_Futures open_at_end (open-&gt;closed 0); NY_Palladium_Futures open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10004,7 +10032,7 @@
         <v>-43.45</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>278844.03</v>
+        <v>275223.99</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -10098,7 +10126,7 @@
         <v>-12.96</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>278888.25</v>
+        <v>275268.21</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -10141,7 +10169,7 @@
         <v>-0.2</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>278901.21</v>
+        <v>275304.35</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -10184,7 +10212,7 @@
         <v>-0.77</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>278887.48</v>
+        <v>275267.45</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -10208,14 +10236,22 @@
           <t>2026-08-06</t>
         </is>
       </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>1</v>
+      </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G85" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="H85" t="n">
-        <v>-0.002</v>
+        <v>-1.007</v>
       </c>
       <c r="I85" s="5" t="n">
         <v>257446.21</v>
@@ -10224,12 +10260,98 @@
         <v>3578.5</v>
       </c>
       <c r="K85" s="6" t="n">
-        <v>-6.12</v>
+        <v>-3602.97</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>278901.41</v>
+        <v>275304.56</v>
       </c>
       <c r="M85" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>253867.71</v>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>3528.76</v>
+      </c>
+      <c r="K86" s="6" t="n">
+        <v>-9.539999999999999</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>275294.82</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>NY_Palladium_Futures</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>250338.95</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>3479.71</v>
+      </c>
+      <c r="K87" s="6" t="n">
+        <v>-13.65</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>275281.17</v>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t>open_at_end</t>
         </is>
